--- a/translations/welsh-translations/xlsx/17-cso-prns-list.xlsx
+++ b/translations/welsh-translations/xlsx/17-cso-prns-list.xlsx
@@ -19,7 +19,7 @@
     <t>Translations with syntax such as {{year}} should be preserved in the translated text, as it's a placeholder for a dynamic value</t>
   </si>
   <si>
-    <t>Reusable content rendered on this page is translated in: 00-shared-layout.xlsx, 15-producer-prns-list.xlsx.</t>
+    <t>Reusable content rendered on this page is translated in: 00-shared-layout.xlsx, 07-producer-certificate-submit.xlsx, 15-producer-prns-list.xlsx.</t>
   </si>
   <si>
     <t>Translation key</t>
